--- a/data/Brienz (BE)/investment_decision/Axalp_MFH_2005-2014_investment_decision.xlsx
+++ b/data/Brienz (BE)/investment_decision/Axalp_MFH_2005-2014_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,41 +460,41 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>4.231310048932445</v>
+        <v>0.9011118495830862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,30 +508,30 @@
         <v>1488.930813074129</v>
       </c>
       <c r="F2" t="n">
-        <v>4.231310048932445</v>
+        <v>0.7658204828858354</v>
       </c>
       <c r="G2" t="n">
         <v>1488.930813074129</v>
       </c>
       <c r="H2" t="n">
-        <v>4.239582736588726</v>
+        <v>0.8028314197370655</v>
       </c>
       <c r="I2" t="n">
         <v>1488.930813074129</v>
       </c>
       <c r="J2" t="n">
-        <v>4.231310048932444</v>
+        <v>0.8391188876987964</v>
       </c>
       <c r="K2" t="n">
         <v>1488.930813074129</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>4.96112344</v>
+        <v>4.690216270496445</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,30 +545,30 @@
         <v>1488.930813074129</v>
       </c>
       <c r="F3" t="n">
-        <v>4.96112344</v>
+        <v>4.690216270496443</v>
       </c>
       <c r="G3" t="n">
         <v>1488.930813074129</v>
       </c>
       <c r="H3" t="n">
-        <v>5.685673940611019</v>
+        <v>4.569405770127601</v>
       </c>
       <c r="I3" t="n">
         <v>1488.930813074129</v>
       </c>
       <c r="J3" t="n">
-        <v>5.569309025507914</v>
+        <v>4.752086591465075</v>
       </c>
       <c r="K3" t="n">
         <v>1488.930813074129</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>4.961123439999999</v>
+        <v>4.690216270496445</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,30 +582,30 @@
         <v>1488.930813074129</v>
       </c>
       <c r="F4" t="n">
-        <v>4.961123439999999</v>
+        <v>4.690216270496443</v>
       </c>
       <c r="G4" t="n">
         <v>1488.930813074129</v>
       </c>
       <c r="H4" t="n">
-        <v>5.685673940611019</v>
+        <v>4.569405770127601</v>
       </c>
       <c r="I4" t="n">
         <v>1488.930813074129</v>
       </c>
       <c r="J4" t="n">
-        <v>5.569309025507914</v>
+        <v>4.752086591465075</v>
       </c>
       <c r="K4" t="n">
         <v>1488.930813074129</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>4.961123439999999</v>
+        <v>4.690216270496445</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,30 +619,30 @@
         <v>1488.930813074129</v>
       </c>
       <c r="F5" t="n">
-        <v>4.961123439999999</v>
+        <v>4.690216270496443</v>
       </c>
       <c r="G5" t="n">
         <v>1488.930813074129</v>
       </c>
       <c r="H5" t="n">
-        <v>5.685673940611019</v>
+        <v>4.569405770127601</v>
       </c>
       <c r="I5" t="n">
         <v>1488.930813074129</v>
       </c>
       <c r="J5" t="n">
-        <v>5.569309025507914</v>
+        <v>4.752086591465076</v>
       </c>
       <c r="K5" t="n">
         <v>1488.930813074129</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>4.961123439999999</v>
+        <v>4.690216270496445</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,26 +656,26 @@
         <v>1488.930813074129</v>
       </c>
       <c r="F6" t="n">
-        <v>4.961123439999999</v>
+        <v>4.690216270496443</v>
       </c>
       <c r="G6" t="n">
         <v>1488.930813074129</v>
       </c>
       <c r="H6" t="n">
-        <v>5.685673940611019</v>
+        <v>4.569405770127601</v>
       </c>
       <c r="I6" t="n">
         <v>1488.930813074129</v>
       </c>
       <c r="J6" t="n">
-        <v>5.569309025507914</v>
+        <v>4.752086591465076</v>
       </c>
       <c r="K6" t="n">
         <v>1488.930813074129</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -684,36 +683,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Axalp_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Axalp_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>2.233396219611194</v>
+        <v>3.173625</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.233396219611194</v>
+        <v>1.693057410979228</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1.191466547328599</v>
+        <v>1.693057410979228</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.191466547328599</v>
+        <v>3.173625</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -721,36 +720,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Axalp_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Axalp_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>2.233396219611194</v>
+        <v>3.173625</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.233396219611194</v>
+        <v>2.22642593991963</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.566817528050983</v>
+        <v>2.22642593991963</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.566817528050983</v>
+        <v>3.173625</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -758,36 +757,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Axalp_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Axalp_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>2.233396219611194</v>
+        <v>3.173625</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.233396219611194</v>
+        <v>2.473775401597474</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.740886409104719</v>
+        <v>2.473775401597474</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.740886409104719</v>
+        <v>3.173625</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -795,36 +794,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Axalp_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Axalp_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>2.233396219611194</v>
+        <v>3.173625</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.233396219611194</v>
+        <v>2.613334306738858</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.83909912521196</v>
+        <v>2.613334306738858</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.83909912521196</v>
+        <v>3.173625</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -832,40 +831,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Axalp_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Axalp_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>2.233396219611194</v>
+        <v>3.173625</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.233396219611194</v>
+        <v>2.702266170589212</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.901683736981264</v>
+        <v>2.702266170589212</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.901683736981264</v>
+        <v>3.173625</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.0004189981123746681</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,30 +878,30 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.00039166764</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0005529425505882353</v>
+        <v>0.00039166764</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.0004200805083613902</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.0004650766582570211</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,30 +915,30 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.0004838247317647058</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0005529425505882353</v>
+        <v>0.0004838247317647066</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0005299032776470535</v>
+        <v>0.0004812806782101837</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.0004650766582570211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,30 +952,30 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.0004838247317646982</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0005529425505882353</v>
+        <v>0.0004838247317647066</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.0004812806782101837</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.000473720289520827</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,30 +989,30 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.0004838247317647058</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0005529425505882353</v>
+        <v>0.0004838247317647058</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0005529425505882313</v>
+        <v>0.0004812806782101729</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.000473720289520827</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,30 +1026,30 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.000529903277647059</v>
+        <v>0.0004838247317647058</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0005529425505882353</v>
+        <v>0.0004838247317647058</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0005529425505882353</v>
+        <v>0.0004812806782101732</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01418576879125832</v>
+        <v>0.03144623562990016</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,30 +1063,30 @@
         <v>0.08225020440000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01418576879125832</v>
+        <v>0.02699483172682743</v>
       </c>
       <c r="G17" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01410821234448068</v>
+        <v>0.02722879760423038</v>
       </c>
       <c r="I17" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01418576879125832</v>
+        <v>0.03188496367595112</v>
       </c>
       <c r="K17" t="n">
         <v>0.08225020440000001</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01931693749107579</v>
+        <v>0.03144623562990016</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,30 +1100,30 @@
         <v>0.08225020440000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01931693749107579</v>
+        <v>0.02699483172682743</v>
       </c>
       <c r="G18" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01931693749107579</v>
+        <v>0.02722879760423038</v>
       </c>
       <c r="I18" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0193169374910758</v>
+        <v>0.03188496367595112</v>
       </c>
       <c r="K18" t="n">
         <v>0.08225020440000001</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01931693749107579</v>
+        <v>0.03144623562990016</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,30 +1137,30 @@
         <v>0.08225020440000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.01931693749107579</v>
+        <v>0.02699483172682743</v>
       </c>
       <c r="G19" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0193169374910758</v>
+        <v>0.02722879760423038</v>
       </c>
       <c r="I19" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0193169374910758</v>
+        <v>0.03188496367595112</v>
       </c>
       <c r="K19" t="n">
         <v>0.08225020440000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.03918911046333604</v>
+        <v>0.03569225006542114</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,30 +1174,30 @@
         <v>0.08225020440000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03918911046333604</v>
+        <v>0.02976110218648154</v>
       </c>
       <c r="G20" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.03918911046333604</v>
+        <v>0.02976110218648154</v>
       </c>
       <c r="I20" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.03918911046333604</v>
+        <v>0.03649554136366419</v>
       </c>
       <c r="K20" t="n">
         <v>0.08225020440000001</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.03405794176351857</v>
+        <v>0.03569225006542115</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,26 +1211,26 @@
         <v>0.08225020440000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.03405794176351857</v>
+        <v>0.02976110218648154</v>
       </c>
       <c r="G21" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.03398038531674092</v>
+        <v>0.02976110218648154</v>
       </c>
       <c r="I21" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.03405794176351856</v>
+        <v>0.03649554136366419</v>
       </c>
       <c r="K21" t="n">
         <v>0.08225020440000001</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1268,7 +1267,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1305,7 +1304,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1342,7 +1341,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1379,7 +1378,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1416,11 +1415,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.006887828310191514</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1434,30 +1433,30 @@
         <v>0.08225020440000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.01212860989714069</v>
       </c>
       <c r="G27" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.0116184807566236</v>
       </c>
       <c r="I27" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.006772823736602291</v>
       </c>
       <c r="K27" t="n">
         <v>0.08225020440000001</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.006887828310191514</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,30 +1470,30 @@
         <v>0.08225020440000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.01212860989714069</v>
       </c>
       <c r="G28" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.0116184807566236</v>
       </c>
       <c r="I28" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.006772823736602291</v>
       </c>
       <c r="K28" t="n">
         <v>0.08225020440000001</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.006887828310191514</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,30 +1507,30 @@
         <v>0.08225020440000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.01212860989714069</v>
       </c>
       <c r="G29" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.0116184807566236</v>
       </c>
       <c r="I29" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.006772823736602291</v>
       </c>
       <c r="K29" t="n">
         <v>0.08225020440000001</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.003521519738412135</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,30 +1544,30 @@
         <v>0.08225020440000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.009452667617351748</v>
       </c>
       <c r="G30" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.009452667617351744</v>
       </c>
       <c r="I30" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.002718228440169093</v>
       </c>
       <c r="K30" t="n">
         <v>0.08225020440000001</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.003521519738412134</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,26 +1581,26 @@
         <v>0.08225020440000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.009452667617351748</v>
       </c>
       <c r="G31" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.009452667617351744</v>
       </c>
       <c r="I31" t="n">
         <v>0.08225020440000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.002718228440169093</v>
       </c>
       <c r="K31" t="n">
         <v>0.08225020440000001</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1638,7 +1637,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1675,7 +1674,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1712,7 +1711,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1749,7 +1748,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1786,7 +1785,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1823,7 +1822,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1860,7 +1859,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1897,7 +1896,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1934,7 +1933,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1971,7 +1970,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -1992,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>1.608908967160116</v>
+        <v>0.6917171841982535</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2004,11 +2003,11 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.6917171841982535</v>
+        <v>1.608908967160116</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2029,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.608908967160116</v>
+        <v>0.9617573388814294</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2041,11 +2040,11 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.9617573388814294</v>
+        <v>1.608908967160116</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2066,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.608908967160116</v>
+        <v>1.101437965962326</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2078,11 +2077,11 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1.101437965962326</v>
+        <v>1.608908967160116</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2103,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.608908967160116</v>
+        <v>1.185725514687129</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2115,11 +2114,11 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1.185725514687129</v>
+        <v>1.608908967160116</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
@@ -2140,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1.608908967160116</v>
+        <v>1.241942180400873</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2152,11 +2151,11 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1.241942180400873</v>
+        <v>1.608908967160116</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2193,7 +2192,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
@@ -2230,7 +2229,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
@@ -2267,7 +2266,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
@@ -2304,7 +2303,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2341,7 +2340,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
@@ -2362,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.49959034034352</v>
+        <v>0.1440392533189279</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2374,15 +2373,15 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1440392533189279</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1513977475190369</v>
+        <v>0.1425558886002445</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,30 +2395,30 @@
         <v>0.49959034034352</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1452817953960662</v>
+        <v>0.1425558886002445</v>
       </c>
       <c r="G53" t="n">
-        <v>0.49959034034352</v>
+        <v>0.2083074442890552</v>
       </c>
       <c r="H53" t="n">
-        <v>0.14484686186287</v>
+        <v>0.1418531953353842</v>
       </c>
       <c r="I53" t="n">
         <v>0.2083074442890552</v>
       </c>
       <c r="J53" t="n">
-        <v>0.149651391244579</v>
+        <v>0.1419938090261931</v>
       </c>
       <c r="K53" t="n">
-        <v>0.2083074442890552</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.1513977475190369</v>
+        <v>0.1436075058043674</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,30 +2432,30 @@
         <v>0.49959034034352</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1452817953960662</v>
+        <v>0.1425558886002445</v>
       </c>
       <c r="G54" t="n">
-        <v>0.49959034034352</v>
+        <v>0.2432509476959253</v>
       </c>
       <c r="H54" t="n">
-        <v>0.14484686186287</v>
+        <v>0.1438452816270407</v>
       </c>
       <c r="I54" t="n">
         <v>0.2432509476959253</v>
       </c>
       <c r="J54" t="n">
-        <v>0.149651391244579</v>
+        <v>0.1419938090261931</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2432509476959253</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1513977475190369</v>
+        <v>0.1436075058043674</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,30 +2469,30 @@
         <v>0.49959034034352</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1452817953960662</v>
+        <v>0.1425558886002445</v>
       </c>
       <c r="G55" t="n">
-        <v>0.49959034034352</v>
+        <v>0.2647613434666218</v>
       </c>
       <c r="H55" t="n">
-        <v>0.14484686186287</v>
+        <v>0.1438452816270407</v>
       </c>
       <c r="I55" t="n">
         <v>0.2647613434666218</v>
       </c>
       <c r="J55" t="n">
-        <v>0.149651391244579</v>
+        <v>0.1419938090261931</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2647613434666218</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1420223211659183</v>
+        <v>0.1390004690831327</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,26 +2506,26 @@
         <v>0.49959034034352</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1409009919241291</v>
+        <v>0.1368685882343816</v>
       </c>
       <c r="G56" t="n">
-        <v>0.49959034034352</v>
+        <v>0.2792063103891668</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1409009919241291</v>
+        <v>0.137050556369639</v>
       </c>
       <c r="I56" t="n">
         <v>0.2792063103891668</v>
       </c>
       <c r="J56" t="n">
-        <v>0.142430182719541</v>
+        <v>0.1377647268067126</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2792063103891668</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2547,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.49959034034352</v>
+        <v>0.1440392533189279</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2559,11 +2558,11 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1440392533189279</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2584,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.49959034034352</v>
+        <v>0.2083074442890552</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2596,11 +2595,11 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2083074442890552</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2621,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.49959034034352</v>
+        <v>0.2432509476959253</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2633,11 +2632,11 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2432509476959253</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2658,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.49959034034352</v>
+        <v>0.2647613434666218</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2670,11 +2669,11 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2647613434666218</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2695,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.49959034034352</v>
+        <v>0.2792063103891668</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2707,11 +2706,11 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2792063103891668</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2748,11 +2747,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.06684008475544198</v>
+        <v>0.03314084595836912</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,30 +2765,30 @@
         <v>0.49959034034352</v>
       </c>
       <c r="F63" t="n">
-        <v>0.07295603687841265</v>
+        <v>0.0327548232482557</v>
       </c>
       <c r="G63" t="n">
         <v>0.49959034034352</v>
       </c>
       <c r="H63" t="n">
-        <v>0.06999463993999472</v>
+        <v>0.0343263306962015</v>
       </c>
       <c r="I63" t="n">
         <v>0.49959034034352</v>
       </c>
       <c r="J63" t="n">
-        <v>0.06573557109783151</v>
+        <v>0.03292434165383007</v>
       </c>
       <c r="K63" t="n">
         <v>0.49959034034352</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.06684008475544198</v>
+        <v>0.03524207389322206</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,30 +2802,30 @@
         <v>0.49959034034352</v>
       </c>
       <c r="F64" t="n">
-        <v>0.07295603687841265</v>
+        <v>0.03601807962456083</v>
       </c>
       <c r="G64" t="n">
         <v>0.49959034034352</v>
       </c>
       <c r="H64" t="n">
-        <v>0.06999463993999472</v>
+        <v>0.03533624159358444</v>
       </c>
       <c r="I64" t="n">
         <v>0.49959034034352</v>
       </c>
       <c r="J64" t="n">
-        <v>0.06573557109783151</v>
+        <v>0.03630641346649185</v>
       </c>
       <c r="K64" t="n">
         <v>0.49959034034352</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.06684008475544199</v>
+        <v>0.03524207389322206</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,30 +2839,30 @@
         <v>0.49959034034352</v>
       </c>
       <c r="F65" t="n">
-        <v>0.07295603687841265</v>
+        <v>0.03601807962456083</v>
       </c>
       <c r="G65" t="n">
         <v>0.49959034034352</v>
       </c>
       <c r="H65" t="n">
-        <v>0.06999463993999472</v>
+        <v>0.03533624159358444</v>
       </c>
       <c r="I65" t="n">
         <v>0.49959034034352</v>
       </c>
       <c r="J65" t="n">
-        <v>0.06573557109783151</v>
+        <v>0.03630641346649185</v>
       </c>
       <c r="K65" t="n">
         <v>0.49959034034352</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.08046951399171333</v>
+        <v>0.05062051338042208</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,26 +2876,26 @@
         <v>0.49959034034352</v>
       </c>
       <c r="F66" t="n">
-        <v>0.08159084323350257</v>
+        <v>0.05046128945738934</v>
       </c>
       <c r="G66" t="n">
         <v>0.49959034034352</v>
       </c>
       <c r="H66" t="n">
-        <v>0.07819451276188842</v>
+        <v>0.05118268243487135</v>
       </c>
       <c r="I66" t="n">
         <v>0.49959034034352</v>
       </c>
       <c r="J66" t="n">
-        <v>0.07721078250602233</v>
+        <v>0.04899759063868234</v>
       </c>
       <c r="K66" t="n">
         <v>0.49959034034352</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2933,7 +2932,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2970,7 +2969,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -3007,7 +3006,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3044,7 +3043,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3081,7 +3080,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3108,17 +3107,17 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.01092152346397425</v>
+        <v>0.49959034034352</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.01092152346397425</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3145,17 +3144,17 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.01903398167891198</v>
+        <v>0.49959034034352</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.01903398167891198</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3182,17 +3181,17 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.02574959891453177</v>
+        <v>0.49959034034352</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.02574959891453177</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3219,17 +3218,17 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.03149710231218487</v>
+        <v>0.49959034034352</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.03149710231218487</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3256,17 +3255,17 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.03650293408390413</v>
+        <v>0.49959034034352</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.03650293408390413</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
@@ -3293,17 +3292,17 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.01092152346397425</v>
+        <v>0.49959034034352</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.01092152346397425</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
@@ -3330,17 +3329,17 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.01903398167891198</v>
+        <v>0.49959034034352</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.01903398167891198</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
@@ -3367,17 +3366,17 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.02574959891453177</v>
+        <v>0.49959034034352</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.02574959891453177</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
@@ -3404,17 +3403,17 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.03149710231218487</v>
+        <v>0.49959034034352</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.03149710231218487</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
@@ -3441,17 +3440,17 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.03650293408390413</v>
+        <v>0.49959034034352</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.03650293408390413</v>
+        <v>0.49959034034352</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B82" t="n">
@@ -3470,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0.2579487541802082</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3482,11 +3481,11 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2579487541802082</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B83" t="n">
@@ -3505,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0.3963962637215035</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3517,11 +3516,11 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.3963962637215035</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B84" t="n">
@@ -3540,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0.4822517236635052</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -3552,11 +3551,11 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.4822517236635052</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B85" t="n">
@@ -3575,7 +3574,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0.5410307300156951</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3587,11 +3586,11 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5410307300156951</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B86" t="n">
@@ -3610,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0.5842634421140054</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -3622,11 +3621,11 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5842634421140054</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B87" t="n">
@@ -3645,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0.2579487541802082</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3657,11 +3656,11 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.2579487541802082</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B88" t="n">
@@ -3680,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0.3963962637215035</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3692,11 +3691,11 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.3963962637215035</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B89" t="n">
@@ -3715,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0.4822517236635052</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3727,11 +3726,11 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.4822517236635052</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B90" t="n">
@@ -3750,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0.5410307300156951</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3762,11 +3761,11 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5410307300156951</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B91" t="n">
@@ -3785,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0.5842634421140054</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3797,11 +3796,11 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5842634421140054</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B92" t="n">
@@ -3820,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0.2579487541802082</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3832,11 +3831,11 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.2579487541802082</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B93" t="n">
@@ -3855,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0.3963962637215035</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3867,11 +3866,11 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.3963962637215035</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B94" t="n">
@@ -3890,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0.4822517236635052</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3902,11 +3901,11 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.4822517236635052</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B95" t="n">
@@ -3925,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0.5410307300156951</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3937,11 +3936,11 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.5410307300156951</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B96" t="n">
@@ -3960,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0.5842634421140054</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3972,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.5842634421140054</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
